--- a/Result/profitability/6508.xlsx
+++ b/Result/profitability/6508.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>0.19</v>
+        <v>0.24375</v>
       </c>
       <c r="N2" t="n">
-        <v>21.18375</v>
+        <v>22.1375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>0.88</v>
       </c>
       <c r="M3" t="n">
-        <v>0.29</v>
+        <v>0.34875</v>
       </c>
       <c r="N3" t="n">
-        <v>21.16625</v>
+        <v>22.9325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.68</v>
       </c>
       <c r="M4" t="n">
-        <v>0.37</v>
+        <v>0.3825</v>
       </c>
       <c r="N4" t="n">
-        <v>21.98125</v>
+        <v>22.08625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>0.335</v>
+        <v>0.43375</v>
       </c>
       <c r="N5" t="n">
-        <v>20.1325</v>
+        <v>21.02625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.415</v>
+        <v>0.46125</v>
       </c>
       <c r="N6" t="n">
-        <v>19.7325</v>
+        <v>20.3475</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4725</v>
+        <v>0.53625</v>
       </c>
       <c r="N7" t="n">
-        <v>19.37625</v>
+        <v>20.15625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0.51125</v>
+        <v>0.53</v>
       </c>
       <c r="N8" t="n">
-        <v>19.21</v>
+        <v>19.63875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.46625</v>
+        <v>0.4662500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>17.48375</v>
@@ -1901,7 +1901,7 @@
         <v>0.21</v>
       </c>
       <c r="M12" t="n">
-        <v>0.40375</v>
+        <v>0.4037500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>17.38375</v>
@@ -9832,6 +9832,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6508</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>447</v>
+      </c>
+      <c r="D75" t="n">
+        <v>326</v>
+      </c>
+      <c r="E75" t="n">
+        <v>121</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>42</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.46%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>55</v>
+      </c>
+      <c r="K75" t="n">
+        <v>44</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.5575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.144909167722856</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.821428571428571</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.150000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3583959899749374</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
